--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/MinimapConstConfig.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/MinimapConstConfig.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -132,6 +132,21 @@
   </si>
   <si>
     <t>#09131EE8</t>
+  </si>
+  <si>
+    <t>Minimap.MarkerIcon.UnitConfig.1005</t>
+  </si>
+  <si>
+    <t>UI-ChatIcon-Battlenet</t>
+  </si>
+  <si>
+    <t>Minimap.SceneFog.VisionRadius</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>SDCMap.Minimap.SceneFog.VisionRadius</t>
   </si>
 </sst>
 </file>
@@ -177,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -366,7 +381,7 @@
         <v>29</v>
       </c>
       <c r="D15" s="0">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16">
@@ -459,6 +474,48 @@
       </c>
       <c r="E22" s="0" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0">
+        <v>19</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="0">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0">
+        <v>20</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="0">
+        <v>8</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0">
+        <v>21</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="0">
+        <v>8</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/MinimapConstConfig.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/MinimapConstConfig.xlsx
@@ -1,18 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -113,6 +128,9 @@
     <t>Minimap.FogCellSize</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>SDCMap.FogCellSize</t>
   </si>
   <si>
@@ -125,13 +143,13 @@
     <t>Minimap.FogColor.Explored</t>
   </si>
   <si>
-    <t>#09131E88</t>
+    <t>#09131EBF</t>
   </si>
   <si>
     <t>Minimap.FogColor.Unexplored</t>
   </si>
   <si>
-    <t>#09131EE8</t>
+    <t>#09131EFF</t>
   </si>
   <si>
     <t>Minimap.MarkerIcon.UnitConfig.1005</t>
@@ -141,9 +159,6 @@
   </si>
   <si>
     <t>Minimap.SceneFog.VisionRadius</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>SDCMap.Minimap.SceneFog.VisionRadius</t>
@@ -152,23 +167,366 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -176,354 +534,1121 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="38.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="0">
+    <row r="5" spans="1:5">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>40</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="0">
+    <row r="6" spans="1:5">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>10</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="0">
+    <row r="7" spans="1:5">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>0</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="0">
+    <row r="8" spans="1:5">
+      <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>0</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="0">
+    <row r="9" spans="1:5">
+      <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>0</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="0">
+    <row r="10" spans="1:5">
+      <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="0">
+      <c r="D10">
         <v>0</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="0">
+    <row r="11" spans="1:5">
+      <c r="B11">
         <v>7</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>40</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="0">
+    <row r="12" spans="1:5">
+      <c r="B12">
         <v>8</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="0">
+    <row r="13" spans="1:5">
+      <c r="B13">
         <v>9</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D13">
         <v>160</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="0">
+    <row r="14" spans="1:5">
+      <c r="B14">
         <v>10</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="0">
+    <row r="15" spans="1:5">
+      <c r="B15">
         <v>11</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>132</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="0">
+    <row r="16" spans="1:5">
+      <c r="B16">
         <v>12</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="0">
+      <c r="D16">
         <v>0</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="0">
+    <row r="17" spans="2:5">
+      <c r="B17">
         <v>13</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>0</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="0">
+    <row r="18" spans="2:5">
+      <c r="B18">
         <v>14</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="0">
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19">
         <v>15</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="0">
-        <v>16</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="0">
-        <v>0</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="0">
-        <v>17</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="0">
-        <v>0</v>
-      </c>
-      <c r="E21" s="0" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="0">
-        <v>18</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="0">
-        <v>0</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="0">
-        <v>19</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="0">
-        <v>0</v>
-      </c>
-      <c r="E23" s="0" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="0">
-        <v>20</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="0">
-        <v>8</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="0">
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25">
         <v>21</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="0">
-        <v>8</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>43</v>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/MinimapConstConfig.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/MinimapConstConfig.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -147,9 +147,6 @@
   </si>
   <si>
     <t>Minimap.FogColor.Unexplored</t>
-  </si>
-  <si>
-    <t>#09131EFF</t>
   </si>
   <si>
     <t>Minimap.MarkerIcon.UnitConfig.1005</t>
@@ -634,154 +631,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" applyFill="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -834,7 +831,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="29">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1025,28 +1022,182 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="19"/>
+      <tableStyleElement type="firstColumn" dxfId="20"/>
+      <tableStyleElement type="lastColumn" dxfId="20"/>
+      <tableStyleElement type="firstRowStripe" dxfId="21"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="21"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="22"/>
+      <tableStyleElement type="totalRow" dxfId="23"/>
+      <tableStyleElement type="firstRowStripe" dxfId="21"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="21"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="24"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="20"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="25"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="26"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="27"/>
+      <tableStyleElement type="pageFieldValues" dxfId="28"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1313,7 +1464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
@@ -1321,329 +1472,329 @@
     <col min="3" max="3" width="38.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="0" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="B5">
+    <row r="5">
+      <c r="B5" s="0">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="B6">
+    <row r="6">
+      <c r="B6" s="0">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="B7">
+    <row r="7">
+      <c r="B7" s="0">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0">
         <v>0</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="B8">
+    <row r="8">
+      <c r="B8" s="0">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="0">
         <v>0</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="0" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="B9">
+    <row r="9">
+      <c r="B9" s="0">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="0">
         <v>0</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="0" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="B10">
+    <row r="10">
+      <c r="B10" s="0">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="0">
         <v>0</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="0" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="B11">
+    <row r="11">
+      <c r="B11" s="0">
         <v>7</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="0">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="B12">
+    <row r="12">
+      <c r="B12" s="0">
         <v>8</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="B13">
+    <row r="13">
+      <c r="B13" s="0">
         <v>9</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="0">
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="B14">
+    <row r="14">
+      <c r="B14" s="0">
         <v>10</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="B15">
+    <row r="15">
+      <c r="B15" s="0">
         <v>11</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="0">
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="B16">
+    <row r="16">
+      <c r="B16" s="0">
         <v>12</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="0">
         <v>0</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="0" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
-      <c r="B17">
+    <row r="17">
+      <c r="B17" s="0">
         <v>13</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="0">
         <v>0</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="0" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
-      <c r="B18">
+    <row r="18">
+      <c r="B18" s="0">
         <v>14</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="0">
         <v>2</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="0" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
-      <c r="B19">
+    <row r="19">
+      <c r="B19" s="0">
         <v>15</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="0">
         <v>0.25</v>
       </c>
     </row>
-    <row r="20" spans="2:5">
-      <c r="B20">
+    <row r="20">
+      <c r="B20" s="0">
         <v>16</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="0">
         <v>0</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="0" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="2:5">
-      <c r="B21">
+    <row r="21">
+      <c r="B21" s="0">
         <v>17</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="0">
         <v>0</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="0" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="2:5">
-      <c r="B22">
+    <row r="22">
+      <c r="B22" s="0">
         <v>18</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="0">
         <v>0</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="0" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0">
+        <v>19</v>
+      </c>
+      <c r="C23" s="0" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23">
-        <v>19</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="D23" s="0">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
+    </row>
+    <row r="24">
+      <c r="B24" s="0">
+        <v>20</v>
+      </c>
+      <c r="C24" s="0" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24">
-        <v>20</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D24" s="0">
+        <v>3</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0">
+        <v>21</v>
+      </c>
+      <c r="C25" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="D24">
+      <c r="D25" s="0">
         <v>3</v>
       </c>
-      <c r="E24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25">
-        <v>21</v>
-      </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="E25" s="0" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1651,4 +1802,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/MinimapConstConfig.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/MinimapConstConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05ET\MatchTest\ETGame\Packages\cn.etetet.statesync\Luban\Config\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421CF908-40EC-4E19-B6AC-ED7E1C44EA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28830" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -159,371 +165,77 @@
   </si>
   <si>
     <t>SDCMap.Minimap.SceneFog.VisionRadius</t>
+  </si>
+  <si>
+    <t>Minimap.PoiIcon.Evacuation</t>
+  </si>
+  <si>
+    <t>poi_evacuation</t>
+  </si>
+  <si>
+    <t>Minimap.PoiIcon.HighContainer</t>
+  </si>
+  <si>
+    <t>poi_high_container</t>
+  </si>
+  <si>
+    <t>Minimap.PoiIcon.BossSpawn</t>
+  </si>
+  <si>
+    <t>poi_boss_spawn</t>
+  </si>
+  <si>
+    <t>Minimap.PoiIcon.Tracked</t>
+  </si>
+  <si>
+    <t>poi_tracked</t>
+  </si>
+  <si>
+    <t>Minimap.PoiTipText.Evacuation</t>
+  </si>
+  <si>
+    <t>Minimap.PoiTipText.HighContainer</t>
+  </si>
+  <si>
+    <t>Minimap.PoiTipText.BossSpawn</t>
+  </si>
+  <si>
+    <t>Minimap.MarkerColor.MissionTask</t>
+  </si>
+  <si>
+    <t>#FF9F1C</t>
+  </si>
+  <si>
+    <t>Minimap.PoiIcon.MissionTask</t>
+  </si>
+  <si>
+    <t>poi_mission_task</t>
+  </si>
+  <si>
+    <t>Minimap.PoiTipText.MissionTask</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -531,338 +243,165 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" applyFill="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="29">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -873,7 +412,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -901,125 +440,8 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1040,7 +462,7 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.3999450666829432"/>
         </horizontal>
       </border>
     </dxf>
@@ -1076,8 +498,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1088,13 +510,13 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.3999450666829432"/>
         </bottom>
       </border>
     </dxf>
@@ -1105,16 +527,16 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
         </patternFill>
       </fill>
       <border>
         <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.3999450666829432"/>
         </top>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.3999450666829432"/>
         </bottom>
       </border>
     </dxf>
@@ -1138,7 +560,7 @@
       </font>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.3999450666829432"/>
         </bottom>
       </border>
     </dxf>
@@ -1153,26 +575,26 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.3999450666829432"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.3999450666829432"/>
         </bottom>
       </border>
     </dxf>
@@ -1203,6 +625,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1460,16 +885,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <sheetPr/>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="38.875" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1778,7 +1203,7 @@
         <v>42</v>
       </c>
       <c r="D24" s="0">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>33</v>
@@ -1792,13 +1217,142 @@
         <v>43</v>
       </c>
       <c r="D25" s="0">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>22</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>23</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>24</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>25</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="0">
+        <v>0</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>26</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="0">
+        <v>38008</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>27</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="0">
+        <v>38009</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>28</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="0">
+        <v>38010</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="0">
+        <v>29</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="0">
+        <v>0</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="0">
+        <v>30</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="0">
+        <v>0</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="0">
+        <v>31</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" s="0">
+        <v>38011</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
